--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -804,7 +804,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11300</v>
+        <v>10200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1080,9 +1080,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C10" s="4">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1106,9 +1112,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1132,9 +1144,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C12" s="4">
+        <v>100</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1158,9 +1176,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1184,9 +1208,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1210,9 +1240,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1236,9 +1272,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C16" s="4">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1262,9 +1304,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45626</v>
+      </c>
+      <c r="C17" s="4">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1288,9 +1336,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45628</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1314,9 +1368,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45628</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1340,9 +1400,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45628</v>
+      </c>
+      <c r="C20" s="4">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -804,7 +804,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>10200</v>
+        <v>9900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1432,9 +1432,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C21" s="4">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1458,9 +1464,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C22" s="4">
+        <v>100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1484,9 +1496,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -97,7 +97,7 @@
     <t>TEACHER</t>
   </si>
   <si>
-    <t>kiranmala</t>
+    <t>Date of completion</t>
   </si>
 </sst>
 </file>
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -274,6 +274,9 @@
     </xf>
     <xf numFmtId="15" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -602,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -620,8 +623,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -696,20 +699,20 @@
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
     <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="23"/>
     </row>
     <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
@@ -804,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2100</v>
+        <v>3700</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -831,7 +834,10 @@
       <c r="F2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="21">
+        <f>B3+G1-1</f>
+        <v>45731</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7" t="s">
@@ -839,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9900</v>
+        <v>8300</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -868,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45643</v>
+      </c>
+      <c r="G3" s="4">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -900,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45645</v>
+      </c>
+      <c r="G4" s="4">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -932,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45645</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -964,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45647</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -996,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45647</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1028,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45649</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1060,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45649</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1528,9 +1576,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45635</v>
+      </c>
+      <c r="C24" s="4">
+        <v>100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1554,9 +1608,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45635</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1580,9 +1640,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45635</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1606,9 +1672,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1632,9 +1704,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1658,9 +1736,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1684,9 +1768,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C30" s="4">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1710,9 +1800,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45643</v>
+      </c>
+      <c r="C31" s="4">
+        <v>100</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1736,9 +1832,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45643</v>
+      </c>
+      <c r="C32" s="4">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3700</v>
+        <v>4200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8300</v>
+        <v>7800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1140,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45651</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1172,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45651</v>
+      </c>
+      <c r="G11" s="4">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1204,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45654</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1236,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45654</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1268,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45654</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7800</v>
+        <v>7700</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1330,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45662</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4300</v>
+        <v>6200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7700</v>
+        <v>5800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45675</v>
+      </c>
+      <c r="K3" s="4">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -924,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45675</v>
+      </c>
+      <c r="K4" s="4">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -1368,9 +1380,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45662</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1400,9 +1418,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1432,9 +1456,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1464,9 +1494,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1496,9 +1532,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G20" s="4">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1528,9 +1570,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1560,9 +1608,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G22" s="4">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1592,9 +1646,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G23" s="4">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1624,9 +1684,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G24" s="4">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1656,9 +1722,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G25" s="4">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1688,9 +1760,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1720,9 +1798,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G27" s="4">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1752,9 +1836,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G28" s="4">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1784,9 +1874,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G29" s="4">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1816,9 +1912,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45673</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1848,9 +1950,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45673</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1880,9 +1988,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45675</v>
+      </c>
+      <c r="G32" s="4">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5800</v>
+        <v>4100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -974,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45678</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1012,9 +1018,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45678</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1050,9 +1062,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45680</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1088,9 +1106,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45680</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1126,9 +1150,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K9" s="4">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1164,9 +1194,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K10" s="4">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1202,9 +1238,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K11" s="4">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1240,9 +1282,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45689</v>
+      </c>
+      <c r="K12" s="4">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1278,9 +1326,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45689</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1316,9 +1370,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45689</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1354,9 +1414,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45689</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1392,9 +1458,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45689</v>
+      </c>
+      <c r="K16" s="4">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1430,9 +1502,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45691</v>
+      </c>
+      <c r="K17" s="4">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1468,9 +1546,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45691</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
@@ -1506,9 +1590,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45691</v>
+      </c>
+      <c r="K19" s="4">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1544,9 +1634,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45691</v>
+      </c>
+      <c r="K20" s="4">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1582,9 +1678,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45691</v>
+      </c>
+      <c r="K21" s="4">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7900</v>
+        <v>8600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4100</v>
+        <v>3400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1722,9 +1722,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K22" s="4">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1760,9 +1766,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K23" s="4">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1798,9 +1810,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K24" s="4">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
@@ -1836,9 +1854,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K25" s="4">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1874,9 +1898,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K26" s="4">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1912,9 +1942,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K27" s="4">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1950,9 +1986,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K28" s="4">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8600</v>
+        <v>9900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>3400</v>
+        <v>2100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45706</v>
+      </c>
+      <c r="O3" s="4">
+        <v>100</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -942,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45706</v>
+      </c>
+      <c r="O4" s="4">
+        <v>100</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -986,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45706</v>
+      </c>
+      <c r="O5" s="4">
+        <v>100</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1030,9 +1048,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45706</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1074,9 +1098,15 @@
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45710</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1118,9 +1148,15 @@
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45710</v>
+      </c>
+      <c r="O8" s="4">
+        <v>100</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1162,9 +1198,15 @@
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>45710</v>
+      </c>
+      <c r="O9" s="4">
+        <v>100</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1206,9 +1248,15 @@
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>45710</v>
+      </c>
+      <c r="O10" s="4">
+        <v>100</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1250,9 +1298,15 @@
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>45710</v>
+      </c>
+      <c r="O11" s="4">
+        <v>100</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2030,9 +2084,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K29" s="4">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -2068,9 +2128,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K30" s="4">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
@@ -2106,9 +2172,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K31" s="4">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2144,9 +2216,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K32" s="4">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>

--- a/LoanOfficer-A/2023/82 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/82 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9900</v>
+        <v>10600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1348,9 +1348,15 @@
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>45714</v>
+      </c>
+      <c r="O12" s="4">
+        <v>100</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1392,9 +1398,15 @@
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>45714</v>
+      </c>
+      <c r="O13" s="4">
+        <v>100</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1436,9 +1448,15 @@
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>45719</v>
+      </c>
+      <c r="O14" s="4">
+        <v>100</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1480,9 +1498,15 @@
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>45719</v>
+      </c>
+      <c r="O15" s="4">
+        <v>100</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1524,9 +1548,15 @@
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>45719</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1568,9 +1598,15 @@
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>45719</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1612,9 +1648,15 @@
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>45719</v>
+      </c>
+      <c r="O18" s="4">
+        <v>100</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
